--- a/utils/monday_sprint_sprint_2023-07.xlsx
+++ b/utils/monday_sprint_sprint_2023-07.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="147">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>6551</t>
+    <t>1478156836</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,22 +87,19 @@
     <t>13/07/2021</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>Não</t>
   </si>
   <si>
     <t>Em Análise</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
     <t>Julho</t>
   </si>
   <si>
-    <t>8342</t>
+    <t>1666445693</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -114,16 +111,16 @@
     <t>13/09/2021</t>
   </si>
   <si>
+    <t>27/03/2023</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>Setembro</t>
   </si>
   <si>
-    <t>19084</t>
+    <t>4109887815</t>
   </si>
   <si>
     <t>Alteração de alçada de aprovação</t>
@@ -135,10 +132,13 @@
     <t>08/03/2023</t>
   </si>
   <si>
+    <t>28/03/2023</t>
+  </si>
+  <si>
     <t>Março</t>
   </si>
   <si>
-    <t>9827</t>
+    <t>4123784623</t>
   </si>
   <si>
     <t>Vincular movimentação do CRP E SPS/PCP.</t>
@@ -147,6 +147,9 @@
     <t>10/03/2023</t>
   </si>
   <si>
+    <t>12/03/2023</t>
+  </si>
+  <si>
     <t>4123956005</t>
   </si>
   <si>
@@ -156,7 +159,10 @@
     <t>Diferenciação de Tipos de OTF/NF em carteira</t>
   </si>
   <si>
-    <t>19109</t>
+    <t>10/04/2023</t>
+  </si>
+  <si>
+    <t>4193800312</t>
   </si>
   <si>
     <t>Romaneio sistema da Portaria</t>
@@ -165,40 +171,52 @@
     <t>23/03/2023</t>
   </si>
   <si>
+    <t>07/04/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>19184</t>
+    <t>4194193999</t>
   </si>
   <si>
     <t>Nova Coluna Planilha MPS (Produção seriada Bloqueada)</t>
   </si>
   <si>
-    <t>19221</t>
+    <t>09/04/2023</t>
+  </si>
+  <si>
+    <t>4194313086</t>
   </si>
   <si>
     <t>Melhoria sistema de movimentação</t>
   </si>
   <si>
-    <t>19230</t>
+    <t>4194334088</t>
   </si>
   <si>
     <t>Gerar 2 tipos de relatório: Carteira Geral de Pedidos - Sistema Carteira / Relatórios / Carteira Geral de pedidos</t>
   </si>
   <si>
-    <t>19232</t>
+    <t>03/04/2023</t>
+  </si>
+  <si>
+    <t>4194354983</t>
   </si>
   <si>
     <t>Melhorias registro Moldagem</t>
   </si>
   <si>
-    <t>19236</t>
+    <t>4194401838</t>
   </si>
   <si>
     <t>Preenchimento do tempo de desmoldagem obrigatório.</t>
   </si>
   <si>
-    <t>19378</t>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>4198267692</t>
   </si>
   <si>
     <t>Reengenharia dos sistemas de expedição - Segunda Onda</t>
@@ -210,25 +228,25 @@
     <t>24/03/2023</t>
   </si>
   <si>
-    <t>19381</t>
+    <t>4198365034</t>
   </si>
   <si>
     <t>Relat. Razão Crítica (Inconsistência 23/03/23)</t>
   </si>
   <si>
-    <t>19382</t>
+    <t>4198392577</t>
   </si>
   <si>
     <t>Setor 556</t>
   </si>
   <si>
-    <t>14075</t>
+    <t>4198444246</t>
   </si>
   <si>
     <t>Contagem duplicada na movimentação</t>
   </si>
   <si>
-    <t>16815</t>
+    <t>4198577563</t>
   </si>
   <si>
     <t>Configurar Prazo Padrão</t>
@@ -237,31 +255,37 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>19384</t>
+    <t>4199557856</t>
   </si>
   <si>
     <t>Distrib. Setores de mesma Seq</t>
   </si>
   <si>
-    <t>19365</t>
+    <t>02/04/2023</t>
+  </si>
+  <si>
+    <t>4199595261</t>
   </si>
   <si>
     <t>Amostra Alto Impacto</t>
   </si>
   <si>
-    <t>19310</t>
+    <t>4199622231</t>
   </si>
   <si>
     <t>Alteração de registro de inspeção</t>
   </si>
   <si>
-    <t>19315</t>
+    <t>05/04/2023</t>
+  </si>
+  <si>
+    <t>4199667457</t>
   </si>
   <si>
     <t>Validação espectro</t>
   </si>
   <si>
-    <t>18704</t>
+    <t>4199734120</t>
   </si>
   <si>
     <t>Correção</t>
@@ -270,37 +294,34 @@
     <t>Fluxo de ACVO Eletrônica</t>
   </si>
   <si>
-    <t>19318</t>
+    <t>4199765718</t>
   </si>
   <si>
     <t>Incluir no relatório requisições de almoxarifado.</t>
   </si>
   <si>
-    <t>19343</t>
+    <t>4199787723</t>
   </si>
   <si>
     <t>Tela de programação - modelação</t>
   </si>
   <si>
-    <t>19342</t>
+    <t>4199825156</t>
   </si>
   <si>
     <t>Alteração sistema de lançamento de CTE</t>
   </si>
   <si>
-    <t>19083</t>
-  </si>
-  <si>
-    <t>19410</t>
+    <t>4200111118</t>
+  </si>
+  <si>
+    <t>4209776244</t>
   </si>
   <si>
     <t>Projeto FATURA - Correção de Agrupamento de Etapas USE</t>
   </si>
   <si>
-    <t>27/03/2023</t>
-  </si>
-  <si>
-    <t>18922</t>
+    <t>4209883532</t>
   </si>
   <si>
     <t>Melhorias SICweb</t>
@@ -342,13 +363,16 @@
     <t>Aplicativo para Imprimir Etiqueta em Impressora Móvel</t>
   </si>
   <si>
+    <t>04/04/2023</t>
+  </si>
+  <si>
     <t>Dashboard de Change Log - Governança de TI</t>
   </si>
   <si>
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-07</t>
+    <t>Jul/2021</t>
   </si>
   <si>
     <t>Base</t>
@@ -403,6 +427,9 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
   </si>
   <si>
     <t>A fazer</t>
@@ -946,33 +973,33 @@
         <v>25</v>
       </c>
       <c r="M2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>20</v>
@@ -984,27 +1011,27 @@
         <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1016,34 +1043,34 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>40</v>
@@ -1081,16 +1108,16 @@
         <v>43</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>40</v>
@@ -1098,25 +1125,25 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1128,16 +1155,16 @@
         <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>40</v>
@@ -1145,7 +1172,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1157,10 +1184,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1172,19 +1199,19 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>40</v>
@@ -1192,7 +1219,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1204,10 +1231,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1219,19 +1246,19 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>40</v>
@@ -1239,7 +1266,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1251,10 +1278,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1266,19 +1293,19 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>40</v>
@@ -1286,7 +1313,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1298,10 +1325,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1313,19 +1340,19 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>40</v>
@@ -1333,7 +1360,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1345,10 +1372,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1360,19 +1387,19 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>40</v>
@@ -1380,7 +1407,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1392,10 +1419,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1407,19 +1434,19 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>40</v>
@@ -1427,46 +1454,46 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L13" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>40</v>
@@ -1474,7 +1501,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1486,10 +1513,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1501,19 +1528,19 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>40</v>
@@ -1521,7 +1548,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1533,10 +1560,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1548,19 +1575,19 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>40</v>
@@ -1568,7 +1595,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1580,10 +1607,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1595,19 +1622,19 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>40</v>
@@ -1615,7 +1642,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1627,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>21</v>
@@ -1642,19 +1669,19 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>40</v>
@@ -1662,7 +1689,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1674,10 +1701,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1689,19 +1716,19 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>40</v>
@@ -1709,7 +1736,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1721,10 +1748,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1736,19 +1763,19 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>40</v>
@@ -1756,7 +1783,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1768,10 +1795,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1783,19 +1810,19 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>40</v>
@@ -1803,7 +1830,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1815,10 +1842,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1830,19 +1857,19 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>40</v>
@@ -1850,22 +1877,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1877,19 +1904,19 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>40</v>
@@ -1897,7 +1924,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1909,13 +1936,13 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>21</v>
@@ -1924,19 +1951,19 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>40</v>
@@ -1944,7 +1971,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1956,10 +1983,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1971,19 +1998,19 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>40</v>
@@ -1991,7 +2018,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2003,13 +2030,13 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -2018,19 +2045,19 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>40</v>
@@ -2038,7 +2065,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2050,13 +2077,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2065,19 +2092,19 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>40</v>
@@ -2085,25 +2112,25 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>21</v>
@@ -2112,19 +2139,19 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>40</v>
@@ -2132,7 +2159,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2144,13 +2171,13 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2159,19 +2186,19 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>40</v>
@@ -2179,25 +2206,25 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>21</v>
@@ -2206,19 +2233,19 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>40</v>
@@ -2226,25 +2253,25 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>21</v>
@@ -2253,19 +2280,19 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>40</v>
@@ -2273,25 +2300,25 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>21</v>
@@ -2300,19 +2327,19 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>40</v>
@@ -2320,25 +2347,25 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>21</v>
@@ -2347,19 +2374,19 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>40</v>
@@ -2367,25 +2394,25 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>21</v>
@@ -2394,19 +2421,19 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>40</v>
@@ -2414,25 +2441,25 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>21</v>
@@ -2441,19 +2468,19 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>40</v>
@@ -2472,23 +2499,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2496,16 +2523,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2516,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>30.03</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2524,7 +2551,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2537,7 +2564,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2545,7 +2572,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2576,12 +2603,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B2">
         <v>33</v>
@@ -2595,7 +2622,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>30.03</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2605,25 +2632,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2640,13 +2667,13 @@
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2658,47 +2685,47 @@
         <v>31</v>
       </c>
       <c r="P10" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11">
         <v>6</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H11">
         <v>7</v>
       </c>
       <c r="J11" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="Q11">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -2710,39 +2737,39 @@
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H13">
         <v>3</v>
       </c>
       <c r="M13" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2750,13 +2777,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H14">
         <v>5</v>
       </c>
       <c r="M14" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2764,7 +2791,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2772,7 +2799,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2788,10 +2815,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2799,7 +2826,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2807,100 +2834,100 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>1786</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1786</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="2">
+        <v>622</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2911,7 +2938,7 @@
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>58</v>
@@ -2919,30 +2946,30 @@
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
